--- a/reports/pdf_change_20260821.xlsx
+++ b/reports/pdf_change_20260821.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="+#,##0;-#,##0;0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,11 +35,6 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -60,21 +55,25 @@
       <color rgb="00C00000"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="000070C0"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -94,6 +93,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -134,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -155,11 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -551,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 41억(0.9%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 6종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -572,229 +588,1013 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억   ·   현금 1억(0.3%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 1종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>코미코  (신규)</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>9522240000</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.04%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>0→420</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-94</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-952182400</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>0.59%→0.37%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>263→169</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>2446080000</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>1.06%→1.59%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>100→149</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>저스템</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-35</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-464464000</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.56%→0.43%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>187→152</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>487656000</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.52%→1.60%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>258→276</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-31</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-447813600</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.67%→0.53%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>201→170</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>536536000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.31%→0.46%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>42→56</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>성호전자</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-464048000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>3.60%→3.30%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>787→764</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>에스티팜</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>1038024000</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>1.15%→1.46%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>50→59</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-484016000</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.39%→0.29%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>49→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>1412320000</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>6.35%→7.11%</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>90→94</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>-305760000</v>
+      </c>
+      <c r="J11" s="16" t="inlineStr">
+        <is>
+          <t>0.16%→0.10%</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>31→19</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>-470496000</v>
+      </c>
+      <c r="J12" s="16" t="inlineStr">
+        <is>
+          <t>1.45%→1.35%</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>173→161</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>씨메스로보틱스</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>-226283200</v>
+      </c>
+      <c r="J13" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.23%</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>64→53</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>로보티즈</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <v>-1365000000</v>
+      </c>
+      <c r="J14" s="16" t="inlineStr">
+        <is>
+          <t>3.42%→2.92%</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>55→50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>-477984000</v>
+      </c>
+      <c r="J15" s="16" t="inlineStr">
+        <is>
+          <t>4.74%→4.61%</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>184→180</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 20억(0.5%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 7종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G19" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>1357519800</v>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>0.83%→1.37%</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>424→564</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>나이벡  (편출)</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n">
+        <v>-527</v>
+      </c>
+      <c r="I20" s="15" t="n">
+        <v>-4443801020</v>
+      </c>
+      <c r="J20" s="16" t="inlineStr">
+        <is>
+          <t>1.16%→0.00%</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>527→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>에이프릴바이오</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>775646250</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>3.64%→3.01%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>999→1,068</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-32</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-390190400</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.69%→0.58%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>222→190</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>앱클론</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>796145000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>2.52%→2.65%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>613→663</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-1077573000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>9.50%→9.92%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>226→220</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>한올바이오파마</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>794769600</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>5.40%→5.68%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>659→683</t>
+        </is>
+      </c>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
+      <c r="J23" s="17" t="n"/>
+      <c r="K23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>에이비엘바이오</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>785565000</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>8.79%→8.93%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>797→815</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
+      <c r="J24" s="17" t="n"/>
+      <c r="K24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>752343800</v>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>7.80%→8.03%</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>540→553</t>
+        </is>
+      </c>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>656224500</v>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>4.87%→5.11%</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>90→93</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
+      <c r="K26" s="17" t="n"/>
+    </row>
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 40억(1.5%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 30억(1.3%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n"/>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="19" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 1종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="8" t="n"/>
+      <c r="J35" s="8" t="n"/>
+      <c r="K35" s="8" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>코미코  (신규)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B37" s="11" t="n">
         <v>395</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C37" s="11" t="n">
         <v>1633088000</v>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>0.00%→5.56%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>0→395</t>
         </is>
       </c>
-      <c r="G14" s="16" t="n"/>
-      <c r="H14" s="16" t="n"/>
-      <c r="I14" s="16" t="n"/>
-      <c r="J14" s="16" t="n"/>
-      <c r="K14" s="16" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억   ·   현금 4억(0.8%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="20" t="n"/>
+      <c r="I42" s="20" t="n"/>
+      <c r="J42" s="20" t="n"/>
+      <c r="K42" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="18">
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A29:K29"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A28:K28"/>
+    <mergeCell ref="A42:K42"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A40:K40"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260821.xlsx
+++ b/reports/pdf_change_20260821.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 41억(0.9%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 6종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,658억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 6종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>420</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>9522240000</v>
+        <v>9476460000</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-94</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-952182400</v>
+        <v>-947604600</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>49</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2446080000</v>
+        <v>2434320000</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-35</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-464464000</v>
+        <v>-462231000</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>18</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>487656000</v>
+        <v>485311500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-31</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-447813600</v>
+        <v>-445660650</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>14</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>536536000</v>
+        <v>533956500</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-23</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-464048000</v>
+        <v>-461817000</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>1038024000</v>
+        <v>1033033500</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-13</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-484016000</v>
+        <v>-481689000</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>4</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1412320000</v>
+        <v>1405530000</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-305760000</v>
+        <v>-468234000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.10%</t>
+          <t>1.45%→1.35%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
@@ -932,23 +932,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-470496000</v>
+        <v>-304290000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.35%</t>
+          <t>0.16%→0.10%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-226283200</v>
+        <v>-225195300</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>-5</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1365000000</v>
+        <v>-1358437500</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>-4</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-477984000</v>
+        <v>-475686000</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
     <row r="17" ht="19" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,820억   ·   현금 20억(0.5%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 7종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,981억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B17" s="4" t="n"/>
@@ -1135,7 +1135,7 @@
         <v>140</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>1357519800</v>
+        <v>1354953600</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>-527</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-4443801020</v>
+        <v>-4435400640</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>69</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>775646250</v>
+        <v>774180000</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>-32</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-390190400</v>
+        <v>-389452800</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>50</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>796145000</v>
+        <v>794640000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>-6</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1077573000</v>
+        <v>-1075536000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
         <v>24</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>794769600</v>
+        <v>793267200</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>18</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>785565000</v>
+        <v>784080000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>752343800</v>
+        <v>750921600</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>656224500</v>
+        <v>654984000</v>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,647억   ·   현금 40억(1.5%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,682억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1396,7 +1396,7 @@
     <row r="31" ht="19" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,208억   ·   현금 30억(1.3%)      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,265억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B31" s="4" t="n"/>
@@ -1420,7 +1420,7 @@
     <row r="34" ht="19" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 277억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 1종목  /  매도 0종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 283억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B34" s="4" t="n"/>
@@ -1516,11 +1516,11 @@
         <v>395</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>1633088000</v>
+        <v>1590112000</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.00%→5.56%</t>
+          <t>0.00%→5.45%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1537,7 +1537,7 @@
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 557억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 570억      당일 2026-08-21  vs  전영업일 2026-08-20      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>

--- a/reports/pdf_change_20260821.xlsx
+++ b/reports/pdf_change_20260821.xlsx
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-468234000</v>
+        <v>-304290000</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.35%</t>
+          <t>0.16%→0.10%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>173→161</t>
+          <t>31→19</t>
         </is>
       </c>
     </row>
@@ -932,23 +932,23 @@
       <c r="E12" s="17" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="H12" s="15" t="n">
         <v>-12</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-304290000</v>
+        <v>-468234000</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>0.16%→0.10%</t>
+          <t>1.45%→1.35%</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>31→19</t>
+          <t>173→161</t>
         </is>
       </c>
     </row>
